--- a/data/TCCHINOOK-25-02-Appendix-B-Escapement-Detailed.xlsx
+++ b/data/TCCHINOOK-25-02-Appendix-B-Escapement-Detailed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://psconline.sharepoint.com/sites/CTC_365/CEME/Annual Reports/C and E Report/2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stephaniepeacock/Library/CloudStorage/Dropbox-SalmonWatersheds/Stephanie Peacock/X Drive/1_PROJECTS/1_Active/State of Salmon/2_Data &amp; Analysis/state-of-salmon/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:40009_{DEF3FFDE-7396-477B-A2A3-E78C91DFBB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A23A433A-61D4-4333-8230-15D3AC90CFFC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B213B4-954A-5045-8079-79515FE47BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40200" yWindow="4860" windowWidth="18580" windowHeight="16520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="127">
   <si>
     <t>Table B1. Southeast Alaska estimates of escapement and coefficients of variation (CVs) of Pacific Salmon Commission Chinook Technical Committee wild Chinook salmon escapement indicator stocks.</t>
   </si>
@@ -964,9 +964,6 @@
   <si>
     <t>Note: Estimates presented in boldface represent estimates generated from direct mark-recapture studies.</t>
   </si>
-  <si>
-    <t>f</t>
-  </si>
 </sst>
 </file>
 
@@ -1171,6 +1168,7 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1735,17 +1733,17 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1806,9 +1804,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1846,7 +1844,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1952,7 +1950,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2094,7 +2092,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2103,14 +2101,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="7" width="6.7265625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="55.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="55.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -2121,7 +2119,7 @@
       <c r="F1" s="29"/>
       <c r="G1" s="29"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
@@ -2138,7 +2136,7 @@
       </c>
       <c r="G2" s="33"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2159,7 +2157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1975</v>
       </c>
@@ -2170,7 +2168,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1976</v>
       </c>
@@ -2183,7 +2181,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1977</v>
       </c>
@@ -2200,7 +2198,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1978</v>
       </c>
@@ -2217,7 +2215,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1979</v>
       </c>
@@ -2234,7 +2232,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1980</v>
       </c>
@@ -2251,7 +2249,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1981</v>
       </c>
@@ -2268,7 +2266,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1982</v>
       </c>
@@ -2285,7 +2283,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1983</v>
       </c>
@@ -2302,7 +2300,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1984</v>
       </c>
@@ -2319,7 +2317,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1985</v>
       </c>
@@ -2336,7 +2334,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1986</v>
       </c>
@@ -2353,7 +2351,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1987</v>
       </c>
@@ -2370,7 +2368,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1988</v>
       </c>
@@ -2389,7 +2387,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1989</v>
       </c>
@@ -2406,7 +2404,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1990</v>
       </c>
@@ -2423,7 +2421,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1991</v>
       </c>
@@ -2446,7 +2444,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1992</v>
       </c>
@@ -2469,7 +2467,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1993</v>
       </c>
@@ -2492,7 +2490,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1994</v>
       </c>
@@ -2515,7 +2513,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1995</v>
       </c>
@@ -2538,7 +2536,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1996</v>
       </c>
@@ -2561,7 +2559,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1997</v>
       </c>
@@ -2584,7 +2582,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1998</v>
       </c>
@@ -2607,7 +2605,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1999</v>
       </c>
@@ -2630,7 +2628,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -2653,7 +2651,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2001</v>
       </c>
@@ -2676,7 +2674,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2002</v>
       </c>
@@ -2699,7 +2697,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2003</v>
       </c>
@@ -2722,7 +2720,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2004</v>
       </c>
@@ -2745,7 +2743,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2005</v>
       </c>
@@ -2766,7 +2764,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2006</v>
       </c>
@@ -2787,7 +2785,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2007</v>
       </c>
@@ -2808,7 +2806,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2008</v>
       </c>
@@ -2829,7 +2827,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2009</v>
       </c>
@@ -2850,7 +2848,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2010</v>
       </c>
@@ -2871,7 +2869,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2011</v>
       </c>
@@ -2892,7 +2890,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2012</v>
       </c>
@@ -2913,7 +2911,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2013</v>
       </c>
@@ -2934,7 +2932,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2014</v>
       </c>
@@ -2955,7 +2953,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2015</v>
       </c>
@@ -2976,7 +2974,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2016</v>
       </c>
@@ -2997,7 +2995,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2017</v>
       </c>
@@ -3018,7 +3016,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2018</v>
       </c>
@@ -3039,7 +3037,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2019</v>
       </c>
@@ -3060,7 +3058,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2020</v>
       </c>
@@ -3081,7 +3079,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2021</v>
       </c>
@@ -3102,7 +3100,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2022</v>
       </c>
@@ -3123,7 +3121,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -3144,7 +3142,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2024</v>
       </c>
@@ -3165,7 +3163,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3182,7 +3180,7 @@
       </c>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
@@ -3199,7 +3197,7 @@
       </c>
       <c r="G55" s="4"/>
     </row>
-    <row r="56" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="28" t="s">
         <v>10</v>
       </c>
@@ -3226,14 +3224,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CB5DF1-CE25-4B11-AD4C-1C1CDA6BC9E8}">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="7" width="6.7265625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="59.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="59.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>118</v>
       </c>
@@ -3244,7 +3242,7 @@
       <c r="F1" s="29"/>
       <c r="G1" s="29"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
@@ -3261,7 +3259,7 @@
       </c>
       <c r="G2" s="33"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -3282,7 +3280,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1975</v>
       </c>
@@ -3305,7 +3303,7 @@
         <v>4548</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1976</v>
       </c>
@@ -3328,7 +3326,7 @@
         <v>8153</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1977</v>
       </c>
@@ -3351,7 +3349,7 @@
         <v>10362</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1978</v>
       </c>
@@ -3374,7 +3372,7 @@
         <v>6879</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1979</v>
       </c>
@@ -3397,7 +3395,7 @@
         <v>8799</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1980</v>
       </c>
@@ -3420,7 +3418,7 @@
         <v>11183</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1981</v>
       </c>
@@ -3443,7 +3441,7 @@
         <v>9342</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1982</v>
       </c>
@@ -3466,7 +3464,7 @@
         <v>11774</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1983</v>
       </c>
@@ -3489,7 +3487,7 @@
         <v>4885</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1984</v>
       </c>
@@ -3512,7 +3510,7 @@
         <v>12437</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1985</v>
       </c>
@@ -3535,7 +3533,7 @@
         <v>15805</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1986</v>
       </c>
@@ -3558,7 +3556,7 @@
         <v>15965</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1987</v>
       </c>
@@ -3581,7 +3579,7 @@
         <v>19411</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1988</v>
       </c>
@@ -3604,7 +3602,7 @@
         <v>44380</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1989</v>
       </c>
@@ -3627,7 +3625,7 @@
         <v>31690</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1990</v>
       </c>
@@ -3650,7 +3648,7 @@
         <v>29593</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1991</v>
       </c>
@@ -3673,7 +3671,7 @@
         <v>29825</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1992</v>
       </c>
@@ -3696,7 +3694,7 @@
         <v>28350</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1993</v>
       </c>
@@ -3719,7 +3717,7 @@
         <v>14012</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1994</v>
       </c>
@@ -3742,7 +3740,7 @@
         <v>25890</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1995</v>
       </c>
@@ -3765,7 +3763,7 @@
         <v>30685</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1996</v>
       </c>
@@ -3788,7 +3786,7 @@
         <v>38249</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1997</v>
       </c>
@@ -3811,7 +3809,7 @@
         <v>26722</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1998</v>
       </c>
@@ -3834,7 +3832,7 @@
         <v>28230</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1999</v>
       </c>
@@ -3857,7 +3855,7 @@
         <v>26665</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -3880,7 +3878,7 @@
         <v>19281</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2001</v>
       </c>
@@ -3903,7 +3901,7 @@
         <v>42768</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2002</v>
       </c>
@@ -3926,7 +3924,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2003</v>
       </c>
@@ -3949,7 +3947,7 @@
         <v>64706</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2004</v>
       </c>
@@ -3972,7 +3970,7 @@
         <v>46420</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2005</v>
       </c>
@@ -3995,7 +3993,7 @@
         <v>21619</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2006</v>
       </c>
@@ -4018,7 +4016,7 @@
         <v>31345</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2007</v>
       </c>
@@ -4041,7 +4039,7 @@
         <v>9721</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2008</v>
       </c>
@@ -4064,7 +4062,7 @@
         <v>12199</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2009</v>
       </c>
@@ -4087,7 +4085,7 @@
         <v>15547</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2010</v>
       </c>
@@ -4110,7 +4108,7 @@
         <v>25710</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2011</v>
       </c>
@@ -4133,7 +4131,7 @@
         <v>36546</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2012</v>
       </c>
@@ -4156,7 +4154,7 @@
         <v>24112</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2013</v>
       </c>
@@ -4179,7 +4177,7 @@
         <v>32226</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2014</v>
       </c>
@@ -4202,7 +4200,7 @@
         <v>34200</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2015</v>
       </c>
@@ -4225,7 +4223,7 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2016</v>
       </c>
@@ -4248,7 +4246,7 @@
         <v>35598</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2017</v>
       </c>
@@ -4271,7 +4269,7 @@
         <v>15141</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2018</v>
       </c>
@@ -4294,7 +4292,7 @@
         <v>7004</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2019</v>
       </c>
@@ -4317,7 +4315,7 @@
         <v>6493</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2020</v>
       </c>
@@ -4340,7 +4338,7 @@
         <v>15641</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2021</v>
       </c>
@@ -4363,7 +4361,7 @@
         <v>7402</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2022</v>
       </c>
@@ -4386,7 +4384,7 @@
         <v>7396</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -4409,7 +4407,7 @@
         <v>12470</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2024</v>
       </c>
@@ -4432,7 +4430,7 @@
         <v>11840</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>41</v>
       </c>
@@ -4464,16 +4462,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE9AF0-6D1D-47F7-882E-4989187DF100}">
   <dimension ref="A1:J55"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="7" width="6.7265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.26953125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="6.7265625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="6.6640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>122</v>
       </c>
@@ -4487,7 +4485,7 @@
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
     </row>
-    <row r="2" spans="1:10" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
@@ -4511,7 +4509,7 @@
       </c>
       <c r="J2" s="33"/>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -4541,7 +4539,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1975</v>
       </c>
@@ -4571,7 +4569,7 @@
       </c>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1976</v>
       </c>
@@ -4601,7 +4599,7 @@
       </c>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1977</v>
       </c>
@@ -4631,7 +4629,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1978</v>
       </c>
@@ -4663,7 +4661,7 @@
         <v>7646</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1979</v>
       </c>
@@ -4695,7 +4693,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1980</v>
       </c>
@@ -4727,7 +4725,7 @@
         <v>4934</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1981</v>
       </c>
@@ -4759,7 +4757,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1982</v>
       </c>
@@ -4791,7 +4789,7 @@
         <v>7910</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1983</v>
       </c>
@@ -4823,7 +4821,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1984</v>
       </c>
@@ -4855,7 +4853,7 @@
         <v>6114</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1985</v>
       </c>
@@ -4887,7 +4885,7 @@
         <v>4918</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1986</v>
       </c>
@@ -4919,7 +4917,7 @@
         <v>6016</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1987</v>
       </c>
@@ -4951,7 +4949,7 @@
         <v>8428</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1988</v>
       </c>
@@ -4983,7 +4981,7 @@
         <v>8956</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1989</v>
       </c>
@@ -5015,7 +5013,7 @@
         <v>9153</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1990</v>
       </c>
@@ -5047,7 +5045,7 @@
         <v>11211</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1991</v>
       </c>
@@ -5079,7 +5077,7 @@
         <v>11899</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1992</v>
       </c>
@@ -5111,7 +5109,7 @@
         <v>20885</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1993</v>
       </c>
@@ -5143,7 +5141,7 @@
         <v>12519</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1994</v>
       </c>
@@ -5175,7 +5173,7 @@
         <v>8218</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1995</v>
       </c>
@@ -5207,7 +5205,7 @@
         <v>17008</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1996</v>
       </c>
@@ -5239,7 +5237,7 @@
         <v>10370</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1997</v>
       </c>
@@ -5271,7 +5269,7 @@
         <v>9551</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1998</v>
       </c>
@@ -5303,7 +5301,7 @@
         <v>12167</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1999</v>
       </c>
@@ -5335,7 +5333,7 @@
         <v>13011</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -5367,7 +5365,7 @@
         <v>9866</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2001</v>
       </c>
@@ -5399,7 +5397,7 @@
         <v>15338</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2002</v>
       </c>
@@ -5431,7 +5429,7 @@
         <v>16421</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2003</v>
       </c>
@@ -5463,7 +5461,7 @@
         <v>22731</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2004</v>
       </c>
@@ -5495,7 +5493,7 @@
         <v>14163</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2005</v>
       </c>
@@ -5527,7 +5525,7 @@
         <v>6710</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2006</v>
       </c>
@@ -5559,7 +5557,7 @@
         <v>9755</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2007</v>
       </c>
@@ -5591,7 +5589,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2008</v>
       </c>
@@ -5623,7 +5621,7 @@
         <v>7028</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2009</v>
       </c>
@@ -5655,7 +5653,7 @@
         <v>16625</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2010</v>
       </c>
@@ -5687,7 +5685,7 @@
         <v>35563</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2011</v>
       </c>
@@ -5719,7 +5717,7 @@
         <v>18530</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2012</v>
       </c>
@@ -5751,7 +5749,7 @@
         <v>11358</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2013</v>
       </c>
@@ -5783,7 +5781,7 @@
         <v>8953</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2014</v>
       </c>
@@ -5815,7 +5813,7 @@
         <v>16852</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2015</v>
       </c>
@@ -5847,7 +5845,7 @@
         <v>21306</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2016</v>
       </c>
@@ -5877,7 +5875,7 @@
         <v>12115</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2017</v>
       </c>
@@ -5909,7 +5907,7 @@
         <v>7787</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2018</v>
       </c>
@@ -5941,7 +5939,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2019</v>
       </c>
@@ -5973,7 +5971,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2020</v>
       </c>
@@ -6005,7 +6003,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2021</v>
       </c>
@@ -6037,7 +6035,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2022</v>
       </c>
@@ -6069,7 +6067,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -6101,7 +6099,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2024</v>
       </c>
@@ -6133,33 +6131,33 @@
         <v>361</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A54" s="36" t="s">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="B54" s="36"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
-    </row>
-    <row r="55" spans="1:10" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="34" t="s">
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+    </row>
+    <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6179,16 +6177,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="6.7265625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="6.7265625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="6.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="55.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="55.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>11</v>
       </c>
@@ -6199,7 +6197,7 @@
       <c r="F1" s="29"/>
       <c r="G1" s="29"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
@@ -6216,7 +6214,7 @@
       </c>
       <c r="G2" s="33"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -6237,7 +6235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1975</v>
       </c>
@@ -6256,7 +6254,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1976</v>
       </c>
@@ -6279,7 +6277,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1977</v>
       </c>
@@ -6302,7 +6300,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1978</v>
       </c>
@@ -6325,7 +6323,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1979</v>
       </c>
@@ -6348,7 +6346,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1980</v>
       </c>
@@ -6371,7 +6369,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1981</v>
       </c>
@@ -6394,7 +6392,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1982</v>
       </c>
@@ -6417,7 +6415,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1983</v>
       </c>
@@ -6440,7 +6438,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1984</v>
       </c>
@@ -6463,7 +6461,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1985</v>
       </c>
@@ -6486,7 +6484,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1986</v>
       </c>
@@ -6509,7 +6507,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1987</v>
       </c>
@@ -6532,7 +6530,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1988</v>
       </c>
@@ -6555,7 +6553,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1989</v>
       </c>
@@ -6578,7 +6576,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1990</v>
       </c>
@@ -6601,7 +6599,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1991</v>
       </c>
@@ -6624,7 +6622,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1992</v>
       </c>
@@ -6647,7 +6645,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1993</v>
       </c>
@@ -6670,7 +6668,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1994</v>
       </c>
@@ -6693,7 +6691,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1995</v>
       </c>
@@ -6716,7 +6714,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1996</v>
       </c>
@@ -6739,7 +6737,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1997</v>
       </c>
@@ -6762,7 +6760,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1998</v>
       </c>
@@ -6785,7 +6783,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1999</v>
       </c>
@@ -6808,7 +6806,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -6831,7 +6829,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2001</v>
       </c>
@@ -6854,7 +6852,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2002</v>
       </c>
@@ -6877,7 +6875,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2003</v>
       </c>
@@ -6900,7 +6898,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2004</v>
       </c>
@@ -6923,7 +6921,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2005</v>
       </c>
@@ -6946,7 +6944,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2006</v>
       </c>
@@ -6969,7 +6967,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2007</v>
       </c>
@@ -6992,7 +6990,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2008</v>
       </c>
@@ -7015,7 +7013,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2009</v>
       </c>
@@ -7038,7 +7036,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2010</v>
       </c>
@@ -7061,7 +7059,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2011</v>
       </c>
@@ -7084,7 +7082,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2012</v>
       </c>
@@ -7107,7 +7105,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2013</v>
       </c>
@@ -7130,7 +7128,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2014</v>
       </c>
@@ -7153,7 +7151,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2015</v>
       </c>
@@ -7176,7 +7174,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2016</v>
       </c>
@@ -7199,7 +7197,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2017</v>
       </c>
@@ -7222,7 +7220,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2018</v>
       </c>
@@ -7245,7 +7243,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2019</v>
       </c>
@@ -7268,7 +7266,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2020</v>
       </c>
@@ -7291,7 +7289,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2021</v>
       </c>
@@ -7314,7 +7312,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2022</v>
       </c>
@@ -7337,7 +7335,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -7360,7 +7358,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2024</v>
       </c>
@@ -7383,7 +7381,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>8</v>
       </c>
@@ -7400,7 +7398,7 @@
       </c>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
@@ -7432,41 +7430,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K59"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.1796875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="6.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.7265625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="2" width="11.1640625" style="1" customWidth="1"/>
+    <col min="3" max="5" width="6.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.6640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="33"/>
       <c r="E2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="35"/>
+      <c r="F2" s="37"/>
       <c r="G2" s="33"/>
       <c r="H2" s="32" t="s">
         <v>18</v>
@@ -7477,19 +7475,19 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="35"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="33"/>
       <c r="E3" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="35"/>
+      <c r="F3" s="37"/>
       <c r="G3" s="33"/>
       <c r="H3" s="32" t="s">
         <v>22</v>
@@ -7502,7 +7500,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
       <c r="B4" s="9" t="s">
         <v>25</v>
@@ -7531,7 +7529,7 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1975</v>
       </c>
@@ -7556,7 +7554,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1976</v>
       </c>
@@ -7581,7 +7579,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1977</v>
       </c>
@@ -7608,7 +7606,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1978</v>
       </c>
@@ -7635,7 +7633,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1979</v>
       </c>
@@ -7662,7 +7660,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1980</v>
       </c>
@@ -7689,7 +7687,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1981</v>
       </c>
@@ -7716,7 +7714,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1982</v>
       </c>
@@ -7743,7 +7741,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1983</v>
       </c>
@@ -7770,7 +7768,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1984</v>
       </c>
@@ -7801,7 +7799,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1985</v>
       </c>
@@ -7832,7 +7830,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1986</v>
       </c>
@@ -7863,7 +7861,7 @@
         <v>7175</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1987</v>
       </c>
@@ -7894,7 +7892,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1988</v>
       </c>
@@ -7925,7 +7923,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1989</v>
       </c>
@@ -7956,7 +7954,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1990</v>
       </c>
@@ -7991,7 +7989,7 @@
         <v>3620</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1991</v>
       </c>
@@ -8026,7 +8024,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1992</v>
       </c>
@@ -8061,7 +8059,7 @@
         <v>8050</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1993</v>
       </c>
@@ -8096,7 +8094,7 @@
         <v>8375</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1994</v>
       </c>
@@ -8131,7 +8129,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1995</v>
       </c>
@@ -8166,7 +8164,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1996</v>
       </c>
@@ -8201,7 +8199,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1997</v>
       </c>
@@ -8236,7 +8234,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1998</v>
       </c>
@@ -8271,7 +8269,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>1999</v>
       </c>
@@ -8306,7 +8304,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2000</v>
       </c>
@@ -8341,7 +8339,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2001</v>
       </c>
@@ -8376,7 +8374,7 @@
         <v>4998</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2002</v>
       </c>
@@ -8411,7 +8409,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2003</v>
       </c>
@@ -8446,7 +8444,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2004</v>
       </c>
@@ -8481,7 +8479,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2005</v>
       </c>
@@ -8516,7 +8514,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2006</v>
       </c>
@@ -8551,7 +8549,7 @@
         <v>3930</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2007</v>
       </c>
@@ -8586,7 +8584,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2008</v>
       </c>
@@ -8621,7 +8619,7 @@
         <v>5530</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2009</v>
       </c>
@@ -8656,7 +8654,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2010</v>
       </c>
@@ -8691,7 +8689,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2011</v>
       </c>
@@ -8726,7 +8724,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2012</v>
       </c>
@@ -8761,7 +8759,7 @@
         <v>4142</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2013</v>
       </c>
@@ -8796,7 +8794,7 @@
         <v>4672</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2014</v>
       </c>
@@ -8831,7 +8829,7 @@
         <v>4193</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2015</v>
       </c>
@@ -8866,7 +8864,7 @@
         <v>5328</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2016</v>
       </c>
@@ -8901,7 +8899,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2017</v>
       </c>
@@ -8936,7 +8934,7 @@
         <v>3438</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2018</v>
       </c>
@@ -8971,7 +8969,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2019</v>
       </c>
@@ -9006,7 +9004,7 @@
         <v>3856</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2020</v>
       </c>
@@ -9041,7 +9039,7 @@
         <v>4427</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2021</v>
       </c>
@@ -9076,7 +9074,7 @@
         <v>3884</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2022</v>
       </c>
@@ -9109,7 +9107,7 @@
         <v>3936</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2023</v>
       </c>
@@ -9142,7 +9140,7 @@
         <v>4152</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2024</v>
       </c>
@@ -9175,88 +9173,83 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A55" s="36" t="s">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="36"/>
-      <c r="K55" s="36"/>
-    </row>
-    <row r="56" spans="1:11" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="37" t="s">
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+    </row>
+    <row r="56" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
-      <c r="K56" s="37"/>
-    </row>
-    <row r="57" spans="1:11" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="37" t="s">
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+    </row>
+    <row r="57" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="37"/>
-      <c r="K57" s="37"/>
-    </row>
-    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+    </row>
+    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
-      <c r="K58" s="37"/>
-    </row>
-    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="37" t="s">
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+    </row>
+    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A57:K57"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -9267,6 +9260,11 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A59:K59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9275,38 +9273,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="7" width="6.7265625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="55.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:7" ht="55.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
       <c r="E2" s="33"/>
       <c r="F2" s="32" t="s">
         <v>37</v>
       </c>
       <c r="G2" s="33"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
@@ -9323,7 +9321,7 @@
       </c>
       <c r="G3" s="33"/>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -9344,7 +9342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1975</v>
       </c>
@@ -9363,7 +9361,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1976</v>
       </c>
@@ -9382,7 +9380,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1977</v>
       </c>
@@ -9401,7 +9399,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1978</v>
       </c>
@@ -9420,7 +9418,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1979</v>
       </c>
@@ -9443,7 +9441,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1980</v>
       </c>
@@ -9466,7 +9464,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1981</v>
       </c>
@@ -9489,7 +9487,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1982</v>
       </c>
@@ -9512,7 +9510,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1983</v>
       </c>
@@ -9535,7 +9533,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1984</v>
       </c>
@@ -9558,7 +9556,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1985</v>
       </c>
@@ -9581,7 +9579,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1986</v>
       </c>
@@ -9604,7 +9602,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1987</v>
       </c>
@@ -9627,7 +9625,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1988</v>
       </c>
@@ -9650,7 +9648,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1989</v>
       </c>
@@ -9673,7 +9671,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1990</v>
       </c>
@@ -9696,7 +9694,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1991</v>
       </c>
@@ -9719,7 +9717,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1992</v>
       </c>
@@ -9742,7 +9740,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1993</v>
       </c>
@@ -9765,7 +9763,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1994</v>
       </c>
@@ -9788,7 +9786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1995</v>
       </c>
@@ -9811,7 +9809,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1996</v>
       </c>
@@ -9834,7 +9832,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1997</v>
       </c>
@@ -9857,7 +9855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1998</v>
       </c>
@@ -9880,7 +9878,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>1999</v>
       </c>
@@ -9903,7 +9901,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2000</v>
       </c>
@@ -9926,7 +9924,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2001</v>
       </c>
@@ -9949,7 +9947,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2002</v>
       </c>
@@ -9972,7 +9970,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2003</v>
       </c>
@@ -9995,7 +9993,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2004</v>
       </c>
@@ -10018,7 +10016,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2005</v>
       </c>
@@ -10041,7 +10039,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2006</v>
       </c>
@@ -10064,7 +10062,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2007</v>
       </c>
@@ -10087,7 +10085,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2008</v>
       </c>
@@ -10110,7 +10108,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2009</v>
       </c>
@@ -10133,7 +10131,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2010</v>
       </c>
@@ -10156,7 +10154,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2011</v>
       </c>
@@ -10179,7 +10177,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2012</v>
       </c>
@@ -10202,7 +10200,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2013</v>
       </c>
@@ -10225,7 +10223,7 @@
         <v>3518</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2014</v>
       </c>
@@ -10248,7 +10246,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2015</v>
       </c>
@@ -10271,7 +10269,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2016</v>
       </c>
@@ -10294,7 +10292,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2017</v>
       </c>
@@ -10317,7 +10315,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2018</v>
       </c>
@@ -10340,7 +10338,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2019</v>
       </c>
@@ -10363,7 +10361,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2020</v>
       </c>
@@ -10386,7 +10384,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2021</v>
       </c>
@@ -10409,7 +10407,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2022</v>
       </c>
@@ -10432,7 +10430,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2023</v>
       </c>
@@ -10455,7 +10453,7 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2024</v>
       </c>
@@ -10465,8 +10463,8 @@
       <c r="C54" s="5">
         <v>5065</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>127</v>
+      <c r="D54" s="5">
+        <v>22938</v>
       </c>
       <c r="E54" s="5">
         <v>25914</v>
@@ -10478,7 +10476,7 @@
         <v>4202</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
@@ -10491,16 +10489,16 @@
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
     </row>
-    <row r="56" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="36" t="s">
+    <row r="56" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -10520,14 +10518,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="11" width="7.7265625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="11" width="7.6640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>43</v>
       </c>
@@ -10542,28 +10540,28 @@
       <c r="J1" s="29"/>
       <c r="K1" s="29"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
       <c r="E2" s="33"/>
       <c r="F2" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="33"/>
       <c r="K2" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="41" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="48" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>47</v>
@@ -10596,7 +10594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1975</v>
       </c>
@@ -10625,7 +10623,7 @@
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1976</v>
       </c>
@@ -10656,7 +10654,7 @@
       </c>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1977</v>
       </c>
@@ -10685,7 +10683,7 @@
       </c>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1978</v>
       </c>
@@ -10716,7 +10714,7 @@
       </c>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1979</v>
       </c>
@@ -10749,7 +10747,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1980</v>
       </c>
@@ -10780,7 +10778,7 @@
         <v>7678</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1981</v>
       </c>
@@ -10813,7 +10811,7 @@
         <v>6516</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1982</v>
       </c>
@@ -10846,7 +10844,7 @@
         <v>7827</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1983</v>
       </c>
@@ -10873,7 +10871,7 @@
         <v>3770</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1984</v>
       </c>
@@ -10898,7 +10896,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1985</v>
       </c>
@@ -10923,7 +10921,7 @@
         <v>4548</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1986</v>
       </c>
@@ -10956,7 +10954,7 @@
         <v>4176</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1987</v>
       </c>
@@ -10989,7 +10987,7 @@
         <v>3774</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1988</v>
       </c>
@@ -11020,7 +11018,7 @@
         <v>6784</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1989</v>
       </c>
@@ -11053,7 +11051,7 @@
         <v>7908</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1990</v>
       </c>
@@ -11078,7 +11076,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1991</v>
       </c>
@@ -11109,7 +11107,7 @@
         <v>8164</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1992</v>
       </c>
@@ -11138,7 +11136,7 @@
         <v>8929</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1993</v>
       </c>
@@ -11173,7 +11171,7 @@
         <v>9980</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1994</v>
       </c>
@@ -11208,7 +11206,7 @@
         <v>8097</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1995</v>
       </c>
@@ -11243,7 +11241,7 @@
         <v>5964</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1996</v>
       </c>
@@ -11278,7 +11276,7 @@
         <v>9449</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1997</v>
       </c>
@@ -11313,7 +11311,7 @@
         <v>11563</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1998</v>
       </c>
@@ -11348,7 +11346,7 @@
         <v>21021</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1999</v>
       </c>
@@ -11383,7 +11381,7 @@
         <v>15779</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -11418,7 +11416,7 @@
         <v>6373</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2001</v>
       </c>
@@ -11453,7 +11451,7 @@
         <v>6811</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2002</v>
       </c>
@@ -11488,7 +11486,7 @@
         <v>11112</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2003</v>
       </c>
@@ -11523,7 +11521,7 @@
         <v>12071</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2004</v>
       </c>
@@ -11558,7 +11556,7 @@
         <v>19790</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2005</v>
       </c>
@@ -11593,7 +11591,7 @@
         <v>7410</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2006</v>
       </c>
@@ -11628,7 +11626,7 @@
         <v>13676</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2007</v>
       </c>
@@ -11663,7 +11661,7 @@
         <v>8039</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2008</v>
       </c>
@@ -11698,7 +11696,7 @@
         <v>7851</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2009</v>
       </c>
@@ -11733,7 +11731,7 @@
         <v>12040</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2010</v>
       </c>
@@ -11768,7 +11766,7 @@
         <v>11482</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2011</v>
       </c>
@@ -11803,7 +11801,7 @@
         <v>10511</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2012</v>
       </c>
@@ -11838,7 +11836,7 @@
         <v>8999</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2013</v>
       </c>
@@ -11873,7 +11871,7 @@
         <v>16670</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2014</v>
       </c>
@@ -11908,7 +11906,7 @@
         <v>11037</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2015</v>
       </c>
@@ -11943,7 +11941,7 @@
         <v>23366</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2016</v>
       </c>
@@ -11978,7 +11976,7 @@
         <v>22006</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2017</v>
       </c>
@@ -12013,7 +12011,7 @@
         <v>17727</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2018</v>
       </c>
@@ -12048,7 +12046,7 @@
         <v>12173</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2019</v>
       </c>
@@ -12083,7 +12081,7 @@
         <v>15891</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2020</v>
       </c>
@@ -12118,7 +12116,7 @@
         <v>12077</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2021</v>
       </c>
@@ -12153,7 +12151,7 @@
         <v>16168</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2022</v>
       </c>
@@ -12188,7 +12186,7 @@
         <v>13377</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -12223,7 +12221,7 @@
         <v>25052</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2024</v>
       </c>
@@ -12258,7 +12256,7 @@
         <v>13101</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="28" t="s">
         <v>57</v>
       </c>
@@ -12288,14 +12286,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R59"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="16" width="7.7265625" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="16" width="7.6640625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>58</v>
       </c>
@@ -12315,7 +12313,7 @@
       <c r="O1" s="29"/>
       <c r="P1" s="29"/>
     </row>
-    <row r="2" spans="1:16" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="40.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
@@ -12355,7 +12353,7 @@
       </c>
       <c r="P2" s="33"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
       <c r="C3" s="31"/>
@@ -12393,7 +12391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1975</v>
       </c>
@@ -12439,7 +12437,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1976</v>
       </c>
@@ -12485,7 +12483,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1977</v>
       </c>
@@ -12531,7 +12529,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1978</v>
       </c>
@@ -12577,7 +12575,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1979</v>
       </c>
@@ -12623,7 +12621,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1980</v>
       </c>
@@ -12669,7 +12667,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1981</v>
       </c>
@@ -12715,7 +12713,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1982</v>
       </c>
@@ -12761,7 +12759,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1983</v>
       </c>
@@ -12807,7 +12805,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1984</v>
       </c>
@@ -12857,7 +12855,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1985</v>
       </c>
@@ -12907,7 +12905,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1986</v>
       </c>
@@ -12957,7 +12955,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1987</v>
       </c>
@@ -13007,7 +13005,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1988</v>
       </c>
@@ -13057,7 +13055,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1989</v>
       </c>
@@ -13107,7 +13105,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1990</v>
       </c>
@@ -13157,7 +13155,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1991</v>
       </c>
@@ -13207,7 +13205,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1992</v>
       </c>
@@ -13257,7 +13255,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1993</v>
       </c>
@@ -13307,7 +13305,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1994</v>
       </c>
@@ -13357,7 +13355,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1995</v>
       </c>
@@ -13405,7 +13403,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1996</v>
       </c>
@@ -13455,7 +13453,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1997</v>
       </c>
@@ -13505,7 +13503,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1998</v>
       </c>
@@ -13555,7 +13553,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1999</v>
       </c>
@@ -13605,7 +13603,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2000</v>
       </c>
@@ -13655,7 +13653,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2001</v>
       </c>
@@ -13705,7 +13703,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2002</v>
       </c>
@@ -13755,7 +13753,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2003</v>
       </c>
@@ -13805,7 +13803,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2004</v>
       </c>
@@ -13855,7 +13853,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2005</v>
       </c>
@@ -13905,7 +13903,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2006</v>
       </c>
@@ -13955,7 +13953,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2007</v>
       </c>
@@ -14005,7 +14003,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2008</v>
       </c>
@@ -14055,7 +14053,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2009</v>
       </c>
@@ -14105,7 +14103,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2010</v>
       </c>
@@ -14155,7 +14153,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2011</v>
       </c>
@@ -14205,7 +14203,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2012</v>
       </c>
@@ -14255,7 +14253,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2013</v>
       </c>
@@ -14305,7 +14303,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2014</v>
       </c>
@@ -14355,7 +14353,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2015</v>
       </c>
@@ -14405,7 +14403,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2016</v>
       </c>
@@ -14455,7 +14453,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2017</v>
       </c>
@@ -14505,7 +14503,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2018</v>
       </c>
@@ -14555,7 +14553,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2019</v>
       </c>
@@ -14605,7 +14603,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2020</v>
       </c>
@@ -14655,7 +14653,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2021</v>
       </c>
@@ -14705,7 +14703,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2022</v>
       </c>
@@ -14755,7 +14753,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -14805,7 +14803,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2024</v>
       </c>
@@ -14855,7 +14853,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>41</v>
       </c>
@@ -14879,110 +14877,117 @@
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A55" s="36" t="s">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A55" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="36"/>
-      <c r="K55" s="36"/>
-      <c r="L55" s="36"/>
-      <c r="M55" s="36"/>
-      <c r="N55" s="36"/>
-      <c r="O55" s="36"/>
-      <c r="P55" s="36"/>
-    </row>
-    <row r="56" spans="1:18" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="37" t="s">
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="34"/>
+      <c r="M55" s="34"/>
+      <c r="N55" s="34"/>
+      <c r="O55" s="34"/>
+      <c r="P55" s="34"/>
+    </row>
+    <row r="56" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
-      <c r="K56" s="37"/>
-      <c r="L56" s="37"/>
-      <c r="M56" s="37"/>
-      <c r="N56" s="37"/>
-      <c r="O56" s="37"/>
-      <c r="P56" s="37"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
       <c r="R56" s="10"/>
     </row>
-    <row r="57" spans="1:18" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="37" t="s">
+    <row r="57" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="37"/>
-      <c r="K57" s="37"/>
-      <c r="L57" s="37"/>
-      <c r="M57" s="37"/>
-      <c r="N57" s="37"/>
-      <c r="O57" s="37"/>
-      <c r="P57" s="37"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+    <row r="58" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
-      <c r="K58" s="37"/>
-      <c r="L58" s="37"/>
-      <c r="M58" s="37"/>
-      <c r="N58" s="37"/>
-      <c r="O58" s="37"/>
-      <c r="P58" s="37"/>
-    </row>
-    <row r="59" spans="1:18" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="37" t="s">
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+    </row>
+    <row r="59" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
-      <c r="L59" s="37"/>
-      <c r="M59" s="37"/>
-      <c r="N59" s="37"/>
-      <c r="O59" s="37"/>
-      <c r="P59" s="37"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A59:P59"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="A55:P55"/>
+    <mergeCell ref="A56:P56"/>
+    <mergeCell ref="A57:P57"/>
+    <mergeCell ref="A58:P58"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -14993,13 +14998,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A59:P59"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="A55:P55"/>
-    <mergeCell ref="A56:P56"/>
-    <mergeCell ref="A57:P57"/>
-    <mergeCell ref="A58:P58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15008,14 +15006,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E52386-A1C4-4A7B-B380-EF8763C47D17}">
   <dimension ref="A1:S60"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" style="1" customWidth="1"/>
-    <col min="2" max="19" width="8.54296875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.1796875" style="1"/>
+    <col min="1" max="1" width="14.33203125" style="1" customWidth="1"/>
+    <col min="2" max="19" width="8.5" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
         <v>74</v>
       </c>
@@ -15038,14 +15036,14 @@
       <c r="R1" s="29"/>
       <c r="S1" s="29"/>
     </row>
-    <row r="2" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="33"/>
       <c r="E2" s="32" t="s">
         <v>76</v>
@@ -15058,12 +15056,12 @@
       <c r="I2" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="35"/>
+      <c r="J2" s="37"/>
       <c r="K2" s="33"/>
       <c r="L2" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="35"/>
+      <c r="M2" s="37"/>
       <c r="N2" s="33"/>
       <c r="O2" s="32" t="s">
         <v>80</v>
@@ -15072,10 +15070,10 @@
       <c r="Q2" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="35"/>
+      <c r="R2" s="37"/>
       <c r="S2" s="33"/>
     </row>
-    <row r="3" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>82</v>
@@ -15132,7 +15130,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>1975</v>
       </c>
@@ -15181,7 +15179,7 @@
         <v>6838</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="16">
         <v>1976</v>
       </c>
@@ -15230,7 +15228,7 @@
         <v>8246</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="16">
         <v>1977</v>
       </c>
@@ -15279,7 +15277,7 @@
         <v>5936</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="16">
         <v>1978</v>
       </c>
@@ -15328,7 +15326,7 @@
         <v>4766</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
         <v>1979</v>
       </c>
@@ -15377,7 +15375,7 @@
         <v>11689</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="16">
         <v>1980</v>
       </c>
@@ -15426,7 +15424,7 @@
         <v>11248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="16">
         <v>1981</v>
       </c>
@@ -15475,7 +15473,7 @@
         <v>5532</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="16">
         <v>1982</v>
       </c>
@@ -15524,7 +15522,7 @@
         <v>4271</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="16">
         <v>1983</v>
       </c>
@@ -15573,7 +15571,7 @@
         <v>14376</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="16">
         <v>1984</v>
       </c>
@@ -15624,7 +15622,7 @@
         <v>5890</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="16">
         <v>1985</v>
       </c>
@@ -15675,7 +15673,7 @@
         <v>7914</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="16">
         <v>1986</v>
       </c>
@@ -15726,7 +15724,7 @@
         <v>6114</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="16">
         <v>1987</v>
       </c>
@@ -15777,7 +15775,7 @@
         <v>12283</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="16">
         <v>1988</v>
       </c>
@@ -15828,7 +15826,7 @@
         <v>9667</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="16">
         <v>1989</v>
       </c>
@@ -15879,7 +15877,7 @@
         <v>15244</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="16">
         <v>1990</v>
       </c>
@@ -15930,7 +15928,7 @@
         <v>15483</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="16">
         <v>1991</v>
       </c>
@@ -15981,7 +15979,7 @@
         <v>15451</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="16">
         <v>1992</v>
       </c>
@@ -16032,7 +16030,7 @@
         <v>10165</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="16">
         <v>1993</v>
       </c>
@@ -16083,7 +16081,7 @@
         <v>5507</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="16">
         <v>1994</v>
       </c>
@@ -16134,7 +16132,7 @@
         <v>8368</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="16">
         <v>1995</v>
       </c>
@@ -16185,7 +16183,7 @@
         <v>9935</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="16">
         <v>1996</v>
       </c>
@@ -16236,7 +16234,7 @@
         <v>8664</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="16">
         <v>1997</v>
       </c>
@@ -16287,7 +16285,7 @@
         <v>7778</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="16">
         <v>1998</v>
       </c>
@@ -16340,7 +16338,7 @@
         <v>7777</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="16">
         <v>1999</v>
       </c>
@@ -16393,7 +16391,7 @@
         <v>8376</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="16">
         <v>2000</v>
       </c>
@@ -16448,7 +16446,7 @@
         <v>6880</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="16">
         <v>2001</v>
       </c>
@@ -16503,7 +16501,7 @@
         <v>9721</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="16">
         <v>2002</v>
       </c>
@@ -16558,7 +16556,7 @@
         <v>11539</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="16">
         <v>2003</v>
       </c>
@@ -16611,7 +16609,7 @@
         <v>7871</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="16">
         <v>2004</v>
       </c>
@@ -16664,7 +16662,7 @@
         <v>13498</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
         <v>2005</v>
       </c>
@@ -16717,7 +16715,7 @@
         <v>2987</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
         <v>2006</v>
       </c>
@@ -16770,7 +16768,7 @@
         <v>8604</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="16">
         <v>2007</v>
       </c>
@@ -16823,7 +16821,7 @@
         <v>7205</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="16">
         <v>2008</v>
       </c>
@@ -16878,7 +16876,7 @@
         <v>10290</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="16">
         <v>2009</v>
       </c>
@@ -16933,7 +16931,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="16">
         <v>2010</v>
       </c>
@@ -16990,7 +16988,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="16">
         <v>2011</v>
       </c>
@@ -17049,7 +17047,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="16">
         <v>2012</v>
       </c>
@@ -17108,7 +17106,7 @@
         <v>3804</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="16">
         <v>2013</v>
       </c>
@@ -17165,7 +17163,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="16">
         <v>2014</v>
       </c>
@@ -17222,7 +17220,7 @@
         <v>2910</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="16">
         <v>2015</v>
       </c>
@@ -17279,7 +17277,7 @@
         <v>4181</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
         <v>2016</v>
       </c>
@@ -17336,7 +17334,7 @@
         <v>10103</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
         <v>2017</v>
       </c>
@@ -17393,7 +17391,7 @@
         <v>10513</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="16">
         <v>2018</v>
       </c>
@@ -17448,7 +17446,7 @@
         <v>10881</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="16">
         <v>2019</v>
       </c>
@@ -17503,7 +17501,7 @@
         <v>3664</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="16">
         <v>2020</v>
       </c>
@@ -17556,7 +17554,7 @@
         <v>6897</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="16">
         <v>2021</v>
       </c>
@@ -17609,7 +17607,7 @@
         <v>3258</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="16">
         <v>2022</v>
       </c>
@@ -17662,7 +17660,7 @@
         <v>8012</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="16">
         <v>2023</v>
       </c>
@@ -17715,7 +17713,7 @@
         <v>3232</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="16">
         <v>2024</v>
       </c>
@@ -17762,7 +17760,7 @@
         <v>10077</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="16" t="s">
         <v>41</v>
       </c>
@@ -17821,146 +17819,152 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A55" s="36" t="s">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A55" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="36"/>
-      <c r="K55" s="36"/>
-      <c r="L55" s="36"/>
-      <c r="M55" s="36"/>
-      <c r="N55" s="36"/>
-      <c r="O55" s="36"/>
-      <c r="P55" s="36"/>
-      <c r="Q55" s="36"/>
-      <c r="R55" s="36"/>
-      <c r="S55" s="36"/>
-    </row>
-    <row r="56" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="37" t="s">
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="34"/>
+      <c r="M55" s="34"/>
+      <c r="N55" s="34"/>
+      <c r="O55" s="34"/>
+      <c r="P55" s="34"/>
+      <c r="Q55" s="34"/>
+      <c r="R55" s="34"/>
+      <c r="S55" s="34"/>
+    </row>
+    <row r="56" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
-      <c r="K56" s="37"/>
-      <c r="L56" s="37"/>
-      <c r="M56" s="37"/>
-      <c r="N56" s="37"/>
-      <c r="O56" s="37"/>
-      <c r="P56" s="37"/>
-      <c r="Q56" s="37"/>
-      <c r="R56" s="37"/>
-      <c r="S56" s="37"/>
-    </row>
-    <row r="57" spans="1:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="A57" s="37" t="s">
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
+    </row>
+    <row r="57" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="37"/>
-      <c r="K57" s="37"/>
-      <c r="L57" s="37"/>
-      <c r="M57" s="37"/>
-      <c r="N57" s="37"/>
-      <c r="O57" s="37"/>
-      <c r="P57" s="37"/>
-      <c r="Q57" s="37"/>
-      <c r="R57" s="37"/>
-      <c r="S57" s="37"/>
-    </row>
-    <row r="58" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="35"/>
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
+    </row>
+    <row r="58" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
-      <c r="K58" s="37"/>
-      <c r="L58" s="37"/>
-      <c r="M58" s="37"/>
-      <c r="N58" s="37"/>
-      <c r="O58" s="37"/>
-      <c r="P58" s="37"/>
-      <c r="Q58" s="37"/>
-      <c r="R58" s="37"/>
-      <c r="S58" s="37"/>
-    </row>
-    <row r="59" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="37" t="s">
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="35"/>
+      <c r="R58" s="35"/>
+      <c r="S58" s="35"/>
+    </row>
+    <row r="59" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
-      <c r="L59" s="37"/>
-      <c r="M59" s="37"/>
-      <c r="N59" s="37"/>
-      <c r="O59" s="37"/>
-      <c r="P59" s="37"/>
-      <c r="Q59" s="37"/>
-      <c r="R59" s="37"/>
-      <c r="S59" s="37"/>
-    </row>
-    <row r="60" spans="1:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="A60" s="37" t="s">
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+    </row>
+    <row r="60" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="37"/>
-      <c r="K60" s="37"/>
-      <c r="L60" s="37"/>
-      <c r="M60" s="37"/>
-      <c r="N60" s="37"/>
-      <c r="O60" s="37"/>
-      <c r="P60" s="37"/>
-      <c r="Q60" s="37"/>
-      <c r="R60" s="37"/>
-      <c r="S60" s="37"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+      <c r="R60" s="35"/>
+      <c r="S60" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A60:S60"/>
+    <mergeCell ref="A55:S55"/>
+    <mergeCell ref="A56:S56"/>
+    <mergeCell ref="A57:S57"/>
+    <mergeCell ref="A58:S58"/>
+    <mergeCell ref="A59:S59"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:D2"/>
@@ -17970,12 +17974,6 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A60:S60"/>
-    <mergeCell ref="A55:S55"/>
-    <mergeCell ref="A56:S56"/>
-    <mergeCell ref="A57:S57"/>
-    <mergeCell ref="A58:S58"/>
-    <mergeCell ref="A59:S59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17984,14 +17982,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC56118-AC31-42E6-A9A6-0EAF30C6CA13}">
   <dimension ref="A1:S54"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="19" width="6.7265625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="19" width="6.6640625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>95</v>
       </c>
@@ -18014,7 +18012,7 @@
       <c r="R1" s="29"/>
       <c r="S1" s="29"/>
     </row>
-    <row r="2" spans="1:19" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
@@ -18055,7 +18053,7 @@
       </c>
       <c r="S2" s="33"/>
     </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>105</v>
@@ -18112,7 +18110,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1976</v>
       </c>
@@ -18167,7 +18165,7 @@
         <v>10754</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1977</v>
       </c>
@@ -18222,7 +18220,7 @@
         <v>16555</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1978</v>
       </c>
@@ -18277,7 +18275,7 @@
         <v>10067</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1979</v>
       </c>
@@ -18332,7 +18330,7 @@
         <v>11789</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1980</v>
       </c>
@@ -18387,7 +18385,7 @@
         <v>24196</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1981</v>
       </c>
@@ -18442,7 +18440,7 @@
         <v>14492</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1982</v>
       </c>
@@ -18497,7 +18495,7 @@
         <v>14914</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1983</v>
       </c>
@@ -18552,7 +18550,7 @@
         <v>10104</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1984</v>
       </c>
@@ -18607,7 +18605,7 @@
         <v>24021</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1985</v>
       </c>
@@ -18662,7 +18660,7 @@
         <v>17264</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1986</v>
       </c>
@@ -18721,7 +18719,7 @@
         <v>23543</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1987</v>
       </c>
@@ -18780,7 +18778,7 @@
         <v>34541</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1988</v>
       </c>
@@ -18839,7 +18837,7 @@
         <v>39877</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1989</v>
       </c>
@@ -18898,7 +18896,7 @@
         <v>56043</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1990</v>
       </c>
@@ -18957,7 +18955,7 @@
         <v>39732</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1991</v>
       </c>
@@ -19016,7 +19014,7 @@
         <v>33289</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1992</v>
       </c>
@@ -19075,7 +19073,7 @@
         <v>33516</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1993</v>
       </c>
@@ -19134,7 +19132,7 @@
         <v>32336</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1994</v>
       </c>
@@ -19193,7 +19191,7 @@
         <v>30728</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1995</v>
       </c>
@@ -19252,7 +19250,7 @@
         <v>31858</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1996</v>
       </c>
@@ -19311,7 +19309,7 @@
         <v>34119</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1997</v>
       </c>
@@ -19370,7 +19368,7 @@
         <v>30929</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1998</v>
       </c>
@@ -19429,7 +19427,7 @@
         <v>20503</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1999</v>
       </c>
@@ -19488,7 +19486,7 @@
         <v>12947</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>2000</v>
       </c>
@@ -19547,7 +19545,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2001</v>
       </c>
@@ -19606,7 +19604,7 @@
         <v>19516</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2002</v>
       </c>
@@ -19665,7 +19663,7 @@
         <v>16647</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2003</v>
       </c>
@@ -19724,7 +19722,7 @@
         <v>22982</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2004</v>
       </c>
@@ -19783,7 +19781,7 @@
         <v>42494</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2005</v>
       </c>
@@ -19842,7 +19840,7 @@
         <v>23309</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2006</v>
       </c>
@@ -19901,7 +19899,7 @@
         <v>24892</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2007</v>
       </c>
@@ -19960,7 +19958,7 @@
         <v>18357</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2008</v>
       </c>
@@ -20019,7 +20017,7 @@
         <v>18927</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2009</v>
       </c>
@@ -20078,7 +20076,7 @@
         <v>14724</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2010</v>
       </c>
@@ -20137,7 +20135,7 @@
         <v>26195</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2011</v>
       </c>
@@ -20196,7 +20194,7 @@
         <v>36507</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2012</v>
       </c>
@@ -20255,7 +20253,7 @@
         <v>25080</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2013</v>
       </c>
@@ -20314,7 +20312,7 @@
         <v>19778</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2014</v>
       </c>
@@ -20373,7 +20371,7 @@
         <v>19995</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2015</v>
       </c>
@@ -20432,7 +20430,7 @@
         <v>34505</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2016</v>
       </c>
@@ -20491,7 +20489,7 @@
         <v>17492</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2017</v>
       </c>
@@ -20550,7 +20548,7 @@
         <v>26383</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2018</v>
       </c>
@@ -20609,7 +20607,7 @@
         <v>28737</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2019</v>
       </c>
@@ -20668,7 +20666,7 @@
         <v>20914</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2020</v>
       </c>
@@ -20727,7 +20725,7 @@
         <v>27548</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2021</v>
       </c>
@@ -20786,7 +20784,7 @@
         <v>19245</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2022</v>
       </c>
@@ -20845,7 +20843,7 @@
         <v>17764</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2023</v>
       </c>
@@ -20904,7 +20902,7 @@
         <v>13812</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2024</v>
       </c>
@@ -20963,7 +20961,7 @@
         <v>18229</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
@@ -20998,7 +20996,7 @@
       </c>
       <c r="S53" s="4"/>
     </row>
-    <row r="54" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="28" t="s">
         <v>106</v>
       </c>
@@ -21044,30 +21042,30 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H58"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1796875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="6.7265625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:8" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:8" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+    </row>
+    <row r="2" spans="1:8" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="32" t="s">
         <v>108</v>
@@ -21076,14 +21074,14 @@
       <c r="D2" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="35"/>
+      <c r="E2" s="37"/>
       <c r="F2" s="33"/>
       <c r="G2" s="32" t="s">
         <v>110</v>
       </c>
       <c r="H2" s="33"/>
     </row>
-    <row r="3" spans="1:8" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
@@ -21103,7 +21101,7 @@
       </c>
       <c r="H3" s="33"/>
     </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -21127,7 +21125,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1975</v>
       </c>
@@ -21151,7 +21149,7 @@
         <v>112500</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1976</v>
       </c>
@@ -21175,7 +21173,7 @@
         <v>115100</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1977</v>
       </c>
@@ -21199,7 +21197,7 @@
         <v>95100</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1978</v>
       </c>
@@ -21223,7 +21221,7 @@
         <v>85300</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1979</v>
       </c>
@@ -21249,7 +21247,7 @@
         <v>89200</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1980</v>
       </c>
@@ -21275,7 +21273,7 @@
         <v>76806</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1981</v>
       </c>
@@ -21301,7 +21299,7 @@
         <v>66603</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1982</v>
       </c>
@@ -21327,7 +21325,7 @@
         <v>78979</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1983</v>
       </c>
@@ -21353,7 +21351,7 @@
         <v>86051</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1984</v>
       </c>
@@ -21379,7 +21377,7 @@
         <v>131369</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1985</v>
       </c>
@@ -21405,7 +21403,7 @@
         <v>196364</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1986</v>
       </c>
@@ -21431,7 +21429,7 @@
         <v>281551</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1987</v>
       </c>
@@ -21457,7 +21455,7 @@
         <v>420656</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1988</v>
       </c>
@@ -21483,7 +21481,7 @@
         <v>339915</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1989</v>
       </c>
@@ -21509,7 +21507,7 @@
         <v>261302</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1990</v>
       </c>
@@ -21535,7 +21533,7 @@
         <v>153593</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1991</v>
       </c>
@@ -21561,7 +21559,7 @@
         <v>103286</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1992</v>
       </c>
@@ -21587,7 +21585,7 @@
         <v>81016</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1993</v>
       </c>
@@ -21613,7 +21611,7 @@
         <v>102908</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1994</v>
       </c>
@@ -21639,7 +21637,7 @@
         <v>132839</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1995</v>
       </c>
@@ -21665,7 +21663,7 @@
         <v>106459</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1996</v>
       </c>
@@ -21691,7 +21689,7 @@
         <v>143118</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1997</v>
       </c>
@@ -21717,7 +21715,7 @@
         <v>161735</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1998</v>
       </c>
@@ -21743,7 +21741,7 @@
         <v>141575</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>1999</v>
       </c>
@@ -21769,7 +21767,7 @@
         <v>165889</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2000</v>
       </c>
@@ -21795,7 +21793,7 @@
         <v>156595</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2001</v>
       </c>
@@ -21821,7 +21819,7 @@
         <v>232366</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2002</v>
       </c>
@@ -21847,7 +21845,7 @@
         <v>279548</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2003</v>
       </c>
@@ -21873,7 +21871,7 @@
         <v>374154</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2004</v>
       </c>
@@ -21899,7 +21897,7 @@
         <v>362804</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2005</v>
       </c>
@@ -21925,7 +21923,7 @@
         <v>277241</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2006</v>
       </c>
@@ -21951,7 +21949,7 @@
         <v>230390</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2007</v>
       </c>
@@ -21977,7 +21975,7 @@
         <v>114001</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2008</v>
       </c>
@@ -22003,7 +22001,7 @@
         <v>197295</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2009</v>
       </c>
@@ -22029,7 +22027,7 @@
         <v>212104</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2010</v>
       </c>
@@ -22055,7 +22053,7 @@
         <v>324908</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2011</v>
       </c>
@@ -22081,7 +22079,7 @@
         <v>322052</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2012</v>
       </c>
@@ -22107,7 +22105,7 @@
         <v>297827</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2013</v>
       </c>
@@ -22133,7 +22131,7 @@
         <v>778254</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2014</v>
       </c>
@@ -22159,7 +22157,7 @@
         <v>684239</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2015</v>
       </c>
@@ -22185,7 +22183,7 @@
         <v>795700</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2016</v>
       </c>
@@ -22211,7 +22209,7 @@
         <v>412851</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2017</v>
       </c>
@@ -22237,7 +22235,7 @@
         <v>297423</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2018</v>
       </c>
@@ -22263,7 +22261,7 @@
         <v>149044</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2019</v>
       </c>
@@ -22289,7 +22287,7 @@
         <v>212238</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2020</v>
       </c>
@@ -22315,7 +22313,7 @@
         <v>299031</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2021</v>
       </c>
@@ -22341,7 +22339,7 @@
         <v>239947</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2022</v>
       </c>
@@ -22367,7 +22365,7 @@
         <v>254881</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2023</v>
       </c>
@@ -22393,7 +22391,7 @@
         <v>338991</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2024</v>
       </c>
@@ -22419,7 +22417,7 @@
         <v>318086</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
@@ -22437,7 +22435,7 @@
       </c>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="28" t="s">
         <v>115</v>
       </c>
@@ -22449,29 +22447,29 @@
       <c r="G56" s="28"/>
       <c r="H56" s="28"/>
     </row>
-    <row r="57" spans="1:8" ht="42.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="37" t="s">
+    <row r="57" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-    </row>
-    <row r="58" spans="1:8" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+    </row>
+    <row r="58" spans="1:8" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -22492,12 +22490,22 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Leader xmlns="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Leader>
+    <Status xmlns="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd">Review Completed</Status>
+    <TaxCatchAll xmlns="e1f7a318-2291-488d-ba6b-c35235b43485" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22735,28 +22743,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Leader xmlns="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Leader>
-    <Status xmlns="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd">Review Completed</Status>
-    <TaxCatchAll xmlns="e1f7a318-2291-488d-ba6b-c35235b43485" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5638C424-E317-48CE-8337-E26339D89CDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25FFDFEB-CE63-48B4-889E-C8319939B4A3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="e1f7a318-2291-488d-ba6b-c35235b43485"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -22781,18 +22788,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25FFDFEB-CE63-48B4-889E-C8319939B4A3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5638C424-E317-48CE-8337-E26339D89CDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="7f5f251d-2d7c-4782-a4d2-b3f0c9d52acd"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="e1f7a318-2291-488d-ba6b-c35235b43485"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>